--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126823255</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>126822920</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>126823677</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126823255</v>
+        <v>126822920</v>
       </c>
       <c r="B2" t="n">
         <v>57658</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476031</v>
+        <v>476163</v>
       </c>
       <c r="R2" t="n">
-        <v>6556392</v>
+        <v>6556412</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -817,7 +817,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126822920</v>
+        <v>126823255</v>
       </c>
       <c r="B3" t="n">
         <v>57658</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476031</v>
       </c>
       <c r="R3" t="n">
-        <v>6556412</v>
+        <v>6556392</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126822920</v>
+        <v>126823255</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476163</v>
+        <v>476031</v>
       </c>
       <c r="R2" t="n">
-        <v>6556412</v>
+        <v>6556392</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126823255</v>
+        <v>126822920</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476031</v>
+        <v>476163</v>
       </c>
       <c r="R3" t="n">
-        <v>6556392</v>
+        <v>6556412</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -962,7 +962,7 @@
         <v>126823677</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126823255</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>126822920</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>126823677</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126823255</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>126822920</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>126823677</v>
       </c>
       <c r="B4" t="n">
-        <v>58027</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 35099-2025 artfynd.xlsx
+++ b/artfynd/A 35099-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126823255</v>
+        <v>126822920</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476031</v>
+        <v>476163</v>
       </c>
       <c r="R2" t="n">
-        <v>6556392</v>
+        <v>6556412</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -817,14 +817,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126822920</v>
+        <v>126823255</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476163</v>
+        <v>476031</v>
       </c>
       <c r="R3" t="n">
-        <v>6556412</v>
+        <v>6556392</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -962,7 +962,7 @@
         <v>126823677</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
